--- a/docs/downloads/04/tbl_class_alaotra_mangabe.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_mangabe.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -486,14 +486,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>11.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -555,7 +549,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
@@ -578,14 +572,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>33.3</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -601,14 +589,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>66.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -627,12 +609,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D12">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>22.9</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -673,34 +649,28 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D15">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>70.40000000000001</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +686,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D16">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +709,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E17">
-        <v>0.6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -757,19 +727,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>48</v>
-      </c>
-      <c r="E18">
-        <v>49.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -785,14 +749,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E19">
-        <v>41.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +772,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>9.300000000000001</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="21">
@@ -826,19 +790,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D21">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>46.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -854,14 +818,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D22">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>34.5</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +841,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D23">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="E23">
-        <v>17.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="24">
@@ -900,14 +864,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="E24">
-        <v>1.8</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="25">
@@ -923,14 +887,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E25">
-        <v>53.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="26">
@@ -946,14 +910,8 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>17</v>
-      </c>
-      <c r="E26">
-        <v>43.6</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -969,14 +927,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E27">
-        <v>2.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="28">
@@ -995,12 +953,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D28">
-        <v>28</v>
-      </c>
-      <c r="E28">
-        <v>12.9</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1041,11 +993,28 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <v>1.8</v>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6-10 ans</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>26</v>
+      </c>
+      <c r="E31">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
